--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-tiflow-op-accept-bundle.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-tiflow-op-accept-bundle.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/StructureDefinition/tiflow-op-accept-bundle</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/tiflow-op-accept-bundle</t>
   </si>
   <si>
     <t>Version</t>
@@ -882,7 +882,7 @@
     <t>Bundle.entry:task.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://gematik.de/fhir/tiflow-core/StructureDefinition/ti-task}
+    <t xml:space="preserve">Task {https://gematik.de/fhir/tiflow/StructureDefinition/ti-task}
 </t>
   </si>
   <si>
